--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/10 Octubre/Liquidacióncvs -oct/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1141" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F471B2F-65E0-43C4-9F82-5E2D74A8186E}"/>
+  <xr:revisionPtr revIDLastSave="1181" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9FB1CD0-67C1-4877-B950-BA83ED412F51}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -160,7 +160,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -208,7 +208,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -544,15 +546,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
   <dimension ref="A1:E155"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>32</v>
       </c>
@@ -569,7 +571,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -586,7 +588,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -603,7 +605,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -620,7 +622,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -637,7 +639,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -654,7 +656,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -671,7 +673,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -688,7 +690,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -705,7 +707,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -722,7 +724,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -739,7 +741,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -750,13 +752,13 @@
         <v>22</v>
       </c>
       <c r="D12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2">
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -773,7 +775,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -790,7 +792,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -807,7 +809,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -824,7 +826,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -835,13 +837,13 @@
         <v>22</v>
       </c>
       <c r="D17" s="2">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E17" s="2">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -858,7 +860,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -875,7 +877,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -892,7 +894,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -909,7 +911,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -926,7 +928,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -943,7 +945,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -960,7 +962,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -977,7 +979,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -994,7 +996,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>37</v>
       </c>
@@ -1011,7 +1013,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -1028,7 +1030,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -1045,7 +1047,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -1062,7 +1064,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -1079,7 +1081,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -1090,13 +1092,13 @@
         <v>22</v>
       </c>
       <c r="D32" s="2">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="E32" s="2">
         <v>3500</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -1113,7 +1115,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1130,7 +1132,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -1147,7 +1149,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1164,7 +1166,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -1181,7 +1183,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -1198,7 +1200,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1215,7 +1217,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>37</v>
       </c>
@@ -1232,7 +1234,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -1249,7 +1251,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -1266,7 +1268,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>37</v>
       </c>
@@ -1283,7 +1285,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>37</v>
       </c>
@@ -1300,7 +1302,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -1317,7 +1319,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>37</v>
       </c>
@@ -1334,7 +1336,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>37</v>
       </c>
@@ -1351,7 +1353,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>37</v>
       </c>
@@ -1368,7 +1370,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>37</v>
       </c>
@@ -1385,7 +1387,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>37</v>
       </c>
@@ -1402,7 +1404,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>37</v>
       </c>
@@ -1419,7 +1421,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>37</v>
       </c>
@@ -1430,13 +1432,13 @@
         <v>22</v>
       </c>
       <c r="D52" s="2">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E52" s="2">
         <v>2000</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>37</v>
       </c>
@@ -1453,7 +1455,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>37</v>
       </c>
@@ -1470,7 +1472,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>37</v>
       </c>
@@ -1487,7 +1489,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>37</v>
       </c>
@@ -1504,7 +1506,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>37</v>
       </c>
@@ -1521,7 +1523,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>37</v>
       </c>
@@ -1538,7 +1540,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>37</v>
       </c>
@@ -1555,7 +1557,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>37</v>
       </c>
@@ -1572,7 +1574,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>37</v>
       </c>
@@ -1589,7 +1591,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>37</v>
       </c>
@@ -1606,7 +1608,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>37</v>
       </c>
@@ -1623,7 +1625,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>37</v>
       </c>
@@ -1640,7 +1642,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>37</v>
       </c>
@@ -1657,7 +1659,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>37</v>
       </c>
@@ -1674,7 +1676,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>37</v>
       </c>
@@ -1691,7 +1693,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>37</v>
       </c>
@@ -1708,7 +1710,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>37</v>
       </c>
@@ -1725,7 +1727,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>37</v>
       </c>
@@ -1742,7 +1744,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>37</v>
       </c>
@@ -1759,7 +1761,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>37</v>
       </c>
@@ -1776,7 +1778,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>37</v>
       </c>
@@ -1793,7 +1795,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>37</v>
       </c>
@@ -1810,7 +1812,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>37</v>
       </c>
@@ -1827,7 +1829,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>37</v>
       </c>
@@ -1844,7 +1846,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>37</v>
       </c>
@@ -1861,7 +1863,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>37</v>
       </c>
@@ -1878,7 +1880,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>37</v>
       </c>
@@ -1895,7 +1897,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>37</v>
       </c>
@@ -1912,7 +1914,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>37</v>
       </c>
@@ -1929,7 +1931,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>37</v>
       </c>
@@ -1940,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="D82" s="2">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="E82" s="2">
         <v>3700</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>37</v>
       </c>
@@ -1963,7 +1965,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>37</v>
       </c>
@@ -1980,7 +1982,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>37</v>
       </c>
@@ -1997,7 +1999,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>37</v>
       </c>
@@ -2014,7 +2016,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>37</v>
       </c>
@@ -2031,7 +2033,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>37</v>
       </c>
@@ -2048,7 +2050,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>37</v>
       </c>
@@ -2065,7 +2067,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>37</v>
       </c>
@@ -2082,7 +2084,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>37</v>
       </c>
@@ -2099,7 +2101,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>37</v>
       </c>
@@ -2116,7 +2118,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>37</v>
       </c>
@@ -2133,7 +2135,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>37</v>
       </c>
@@ -2150,7 +2152,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>37</v>
       </c>
@@ -2167,7 +2169,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>37</v>
       </c>
@@ -2184,7 +2186,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>37</v>
       </c>
@@ -2201,7 +2203,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>37</v>
       </c>
@@ -2218,7 +2220,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>37</v>
       </c>
@@ -2235,7 +2237,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>37</v>
       </c>
@@ -2252,7 +2254,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>37</v>
       </c>
@@ -2269,7 +2271,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>37</v>
       </c>
@@ -2280,13 +2282,13 @@
         <v>22</v>
       </c>
       <c r="D102" s="2">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="E102" s="2">
         <v>2600</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>37</v>
       </c>
@@ -2303,7 +2305,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>37</v>
       </c>
@@ -2320,7 +2322,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>37</v>
       </c>
@@ -2337,7 +2339,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>37</v>
       </c>
@@ -2354,7 +2356,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>37</v>
       </c>
@@ -2365,13 +2367,13 @@
         <v>22</v>
       </c>
       <c r="D107" s="2">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="E107" s="2">
         <v>2200</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>37</v>
       </c>
@@ -2388,7 +2390,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>37</v>
       </c>
@@ -2405,7 +2407,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>37</v>
       </c>
@@ -2422,7 +2424,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>37</v>
       </c>
@@ -2439,7 +2441,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>37</v>
       </c>
@@ -2450,13 +2452,13 @@
         <v>22</v>
       </c>
       <c r="D112" s="2">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E112" s="2">
         <v>1000</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>37</v>
       </c>
@@ -2473,7 +2475,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>37</v>
       </c>
@@ -2490,7 +2492,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>37</v>
       </c>
@@ -2507,7 +2509,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>37</v>
       </c>
@@ -2524,7 +2526,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>37</v>
       </c>
@@ -2535,13 +2537,13 @@
         <v>22</v>
       </c>
       <c r="D117" s="2">
-        <v>27700</v>
+        <v>25521</v>
       </c>
       <c r="E117" s="2">
         <v>54750</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>37</v>
       </c>
@@ -2558,7 +2560,7 @@
         <v>54750</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>37</v>
       </c>
@@ -2575,7 +2577,7 @@
         <v>54750</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>37</v>
       </c>
@@ -2592,7 +2594,7 @@
         <v>54750</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>37</v>
       </c>
@@ -2609,7 +2611,7 @@
         <v>54750</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>37</v>
       </c>
@@ -2620,13 +2622,13 @@
         <v>22</v>
       </c>
       <c r="D122" s="2">
-        <v>27700</v>
+        <v>1</v>
       </c>
       <c r="E122" s="2">
-        <v>54750</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+        <v>54450</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>37</v>
       </c>
@@ -2640,10 +2642,10 @@
         <v>930</v>
       </c>
       <c r="E123" s="2">
-        <v>54750</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+        <v>54450</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>37</v>
       </c>
@@ -2657,10 +2659,10 @@
         <v>153</v>
       </c>
       <c r="E124" s="2">
-        <v>54750</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+        <v>54450</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>37</v>
       </c>
@@ -2674,10 +2676,10 @@
         <v>1712</v>
       </c>
       <c r="E125" s="2">
-        <v>54750</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+        <v>54450</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>37</v>
       </c>
@@ -2691,10 +2693,10 @@
         <v>3360</v>
       </c>
       <c r="E126" s="2">
-        <v>54750</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+        <v>54450</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>37</v>
       </c>
@@ -2711,7 +2713,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>37</v>
       </c>
@@ -2728,7 +2730,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>37</v>
       </c>
@@ -2745,7 +2747,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>37</v>
       </c>
@@ -2762,7 +2764,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>37</v>
       </c>
@@ -2779,7 +2781,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>37</v>
       </c>
@@ -2796,7 +2798,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>37</v>
       </c>
@@ -2813,7 +2815,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>37</v>
       </c>
@@ -2830,7 +2832,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>37</v>
       </c>
@@ -2847,7 +2849,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>37</v>
       </c>
@@ -2864,7 +2866,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>37</v>
       </c>
@@ -2881,7 +2883,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>37</v>
       </c>
@@ -2898,7 +2900,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>37</v>
       </c>
@@ -2915,7 +2917,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>37</v>
       </c>
@@ -2932,7 +2934,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>37</v>
       </c>
@@ -2949,7 +2951,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>37</v>
       </c>
@@ -2966,7 +2968,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>37</v>
       </c>
@@ -2983,7 +2985,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>37</v>
       </c>
@@ -3000,7 +3002,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>37</v>
       </c>
@@ -3017,7 +3019,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>37</v>
       </c>
@@ -3034,7 +3036,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>37</v>
       </c>
@@ -3051,7 +3053,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>37</v>
       </c>
@@ -3068,7 +3070,7 @@
         <v>54750</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>37</v>
       </c>
@@ -3082,10 +3084,10 @@
         <v>100000</v>
       </c>
       <c r="E149" s="2">
-        <v>54750</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+        <v>54450</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>37</v>
       </c>
@@ -3096,13 +3098,13 @@
         <v>22</v>
       </c>
       <c r="D150" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" s="2">
         <v>1000</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>37</v>
       </c>
@@ -3119,7 +3121,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>37</v>
       </c>
@@ -3136,7 +3138,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>37</v>
       </c>
@@ -3153,7 +3155,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>37</v>
       </c>
@@ -3170,7 +3172,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>37</v>
       </c>

--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/10 Octubre/Liquidacióncvs -oct/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1181" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9FB1CD0-67C1-4877-B950-BA83ED412F51}"/>
+  <xr:revisionPtr revIDLastSave="1183" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{734493A4-59C7-447B-A221-4F8EEFBB60F5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -546,15 +546,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
   <dimension ref="A1:E155"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>32</v>
       </c>
@@ -571,7 +571,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -588,7 +588,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -605,7 +605,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -622,7 +622,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -639,7 +639,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -656,7 +656,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -673,7 +673,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -690,7 +690,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -707,7 +707,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -724,7 +724,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -741,7 +741,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -758,7 +758,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -775,7 +775,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -792,7 +792,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -809,7 +809,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -826,7 +826,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -843,7 +843,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -860,7 +860,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -877,7 +877,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -894,7 +894,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -911,7 +911,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -928,7 +928,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -945,7 +945,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -962,7 +962,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -979,7 +979,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -996,7 +996,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>37</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>37</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -1149,7 +1149,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>37</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>37</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>37</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>37</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>37</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>37</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>37</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>37</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>37</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>37</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>37</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>37</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>37</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>37</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>37</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>37</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>37</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>37</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>37</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>37</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>37</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>37</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>37</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>37</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>37</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>37</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>37</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>37</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>37</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>37</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>37</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>37</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>37</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>37</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>37</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>37</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>37</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>37</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>37</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>37</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>37</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>37</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>37</v>
       </c>
@@ -1999,7 +1999,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>37</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>37</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>37</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>37</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>37</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>37</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>37</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>37</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>37</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>37</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>37</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>37</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>37</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>37</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>37</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>37</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>37</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>37</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>37</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>37</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>37</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>37</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>37</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>37</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>37</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>37</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>37</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>37</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>37</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>37</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>37</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>37</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>54750</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>37</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>54750</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>37</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>54750</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>37</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>54750</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>37</v>
       </c>
@@ -2611,7 +2611,7 @@
         <v>54750</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>37</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>54450</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>37</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>54450</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>37</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>54450</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>37</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>54450</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>37</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>54450</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>37</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>37</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>37</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>37</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>37</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>37</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>37</v>
       </c>
@@ -2815,7 +2815,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>37</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>37</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>37</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>37</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>37</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>37</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>37</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>37</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>37</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>37</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>37</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>37</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>37</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>37</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>37</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>54750</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>37</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>54450</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>37</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>37</v>
       </c>
@@ -3121,7 +3121,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>37</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>37</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>37</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>37</v>
       </c>
